--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04835000038146973</v>
+        <v>0.04998000144958496</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04998000144958496</v>
+        <v>0.05302000045776367</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05302000045776367</v>
+        <v>0.05217999935150146</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05217999935150146</v>
+        <v>0.05276999950408936</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05341000080108643</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05341000080108643</v>
+        <v>0.05276999950408936</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05238999843597412</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05238999843597412</v>
+        <v>0.05245999813079834</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05245999813079834</v>
+        <v>0.0524399995803833</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.0524399995803833</v>
+        <v>0.05240000247955322</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05220999717712402</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05220999717712402</v>
+        <v>0.05085000038146972</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05085000038146972</v>
+        <v>0.05105999946594238</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-17 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05105999946594238</v>
+        <v>0.05098000049591064</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-17 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05098000049591064</v>
+        <v>0.0514799976348877</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.0514799976348877</v>
+        <v>0.05126999855041504</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-20 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05126999855041504</v>
+        <v>0.05105999946594238</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05105999946594238</v>
+        <v>0.04963000297546387</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04991999626159668</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04991999626159668</v>
+        <v>0.0498799991607666</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.0498199987411499</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.0498199987411499</v>
+        <v>0.04993000030517578</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04993000030517578</v>
+        <v>0.05015999794006348</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.05015999794006348</v>
+        <v>0.04994999885559082</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04994999885559082</v>
+        <v>0.04933000087738037</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/NONE_research.xlsx
+++ b/app/reports/NONE_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-31 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04933000087738037</v>
+        <v>0.04928999900817871</v>
       </c>
     </row>
     <row r="6">
